--- a/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino est à l'école. La classe range les crayons. Le couloir sent le savon. Zoé laisse tomber un crayon. Un camarade commence à rire. Le rire est court. Nino ne rit pas. Il ne faut pas rire. Nino ne répète pas. Il ne faut pas répéter. Nino dit : ce n'est pas gentil. Il va vers Zoé. Il ramasse le crayon. Il le tend. Zoé le reprend. La maîtresse s'approche. Le camarade dit : pardon. Plus tard, Nino est au parc avec maman. Un enfant laisse tomber son gant. Un autre commence à rire. Le rire est court. Nino se souvient. Il ne rit pas. Il ne répète pas. Il dit : ce n'est pas gentil. Il tend le gant. Maman dit : tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Nino serre la main de maman.</t>
+          <t>Nino est à l'école. La classe range les crayons. Le couloir sent le savon. Zoé laisse tomber un crayon. Un camarade commence à rire. Le rire est court. Nino ne rit pas. Il ne faut pas rire. Nino ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Il va vers Zoé. Il ramasse le crayon. Il le tend. Zoé le reprend. La maîtresse s'approche. Le Pardon. Plus tard, Nino est au parc avec maman. Un enfant laisse tomber son gant. Un autre commence à rire. Le rire est court. Nino se souvient. Il ne rit pas. Il ne répète pas. Ce n'est pas gentil. Il tend le gant. Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Nino serre la main de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nino est à l'école. La classe range les crayons. Le couloir sent le savon. Zoé laisse tomber un crayon. Un camarade commence à rire. Le rire est court. Nino ne rit pas. Il ne faut pas rire. Nino ne répète pas. Il ne faut pas répéter.
+enfant-m|Ce n'est pas gentil. Il va vers Zoé. Il ramasse le crayon. Il le tend.
+narrateur|Zoé le reprend. La maîtresse s'approche. Le
+enfant-f|Pardon. Plus tard, Nino est au parc avec maman.
+narrateur|Un enfant laisse tomber son gant. Un autre commence à rire. Le rire est court. Nino se souvient. Il ne rit pas. Il ne répète pas.
+narrateur|Ce n'est pas gentil. Il tend le gant.
+maman|Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter.
+narrateur|Ce n'est pas gentil.
+narrateur|Nino serre la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1496,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade rit. Que fait Nino ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1525,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis au parc.</t>
+          <t>Nino n'a pas ri. Il n'a pas répété. Il Ce n'est pas gentil. À l'école, puis au parc.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1667,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nino n'a pas ri. Il n'a pas répété. Il
+enfant-f|Ce n'est pas gentil. À l'école, puis au parc.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Nino range son cartable. Maman marche à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,11 @@
 narrateur|Nino serre la main de maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Un camarade rit. Que fait Nino ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1684,11 @@
 enfant-f|Ce n'est pas gentil. À l'école, puis au parc.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1852,7 @@
           <t>narrateur|Nino range son cartable. Maman marche à côté.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2020,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2063,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2278,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nino ne rit pas, deux fois</t>
+          <t>Le crayon et le gant de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un crayon tombe en classe, puis un gant au parc. Nino n'est pas là pour rire. Il ramasse, il tend, deux fois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Nino est à l'école. La classe range les crayons. Le couloir sent le savon. Zoé laisse tomber un crayon. Un camarade commence à rire. Le rire est court. Nino ne rit pas. Il ne faut pas rire. Nino ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Il va vers Zoé. Il ramasse le crayon. Il le tend. Zoé le reprend. La maîtresse s'approche. Le Pardon. Plus tard, Nino est au parc avec maman. Un enfant laisse tomber son gant. Un autre commence à rire. Le rire est court. Nino se souvient. Il ne rit pas. Il ne répète pas. Ce n'est pas gentil. Il tend le gant. Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Nino serre la main de maman.</t>
+          <t>Un rayon de poussière danse au-dessus des crayons. La boîte en bois est chaude au soleil. Ça sent le crayon gras et le savon. Le plancher craque un peu. Nino, ta veste est sur le crochet. Tu as vu le rayon sur les crayons ? Oui, maman. Il brille. Je reviens te chercher après l'école. On ira au parc. D'accord. En ce moment, la classe range les crayons. Sarah tient un crayon jaune. Le bois est lisse. Le crayon glisse. Il tombe près de la boîte. Un camarade commence un petit rire. Le rire est court. Nino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Sarah. Il ramasse le crayon. Il le tend. Merci, Nino. Sarah reprend le crayon. Elle le pose dans la boîte, tout droit. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, le parc sent l'herbe coupée. Une chaîne de balançoire tinte, loin. Un grain de sable brille sur le bac. Maman tient le gant de Nino. Tu te souviens du crayon ? Oui. On ramasse. Sarah laisse tomber son gant bleu. Le gant est mou, près du bac. Un autre petit rire commence. Le rire est court. Nino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il tend le gant. Merci. Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. C'est du bon travail, Nino. Tu as du sable sur les genoux ? Un peu. On le secoue. Nino serre la main de maman. Le gant bleu est remis. Le rayon du matin n'est plus là. Il reste l'herbe, et le calme. On rentre tout doux ? Oui, maman. Un oiseau crie, puis plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,71 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Nino est à l'école. La classe range les crayons. Le couloir sent le savon. Zoé laisse tomber un crayon. Un camarade commence à rire. Le rire est court. Nino ne rit pas. Il ne faut pas rire. Nino ne répète pas. Il ne faut pas répéter.
-enfant-m|Ce n'est pas gentil. Il va vers Zoé. Il ramasse le crayon. Il le tend.
-narrateur|Zoé le reprend. La maîtresse s'approche. Le
-enfant-f|Pardon. Plus tard, Nino est au parc avec maman.
-narrateur|Un enfant laisse tomber son gant. Un autre commence à rire. Le rire est court. Nino se souvient. Il ne rit pas. Il ne répète pas.
-narrateur|Ce n'est pas gentil. Il tend le gant.
-maman|Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter.
-narrateur|Ce n'est pas gentil.
-narrateur|Nino serre la main de maman.</t>
+          <t>narrateur|Un rayon de poussière danse au-dessus des crayons.
+narrateur|La boîte en bois est chaude au soleil.
+narrateur|Ça sent le crayon gras et le savon.
+narrateur|Le plancher craque un peu.
+maman|Nino, ta veste est sur le crochet.
+maman|Tu as vu le rayon sur les crayons ?
+enfant-m|Oui, maman.
+enfant-m|Il brille.
+maman|Je reviens te chercher après l'école.
+maman|On ira au parc.
+enfant-m|D'accord.
+narrateur|En ce moment, la classe range les crayons.
+narrateur|Sarah tient un crayon jaune.
+narrateur|Le bois est lisse.
+narrateur|Le crayon glisse.
+narrateur|Il tombe près de la boîte.
+narrateur|Un camarade commence un petit rire.
+narrateur|Le rire est court.
+narrateur|Nino n'est pas là pour rire.
+narrateur|Il ne répète pas.
+enfant-m|Ce n'est pas gentil.
+narrateur|Il va vers Sarah.
+narrateur|Il ramasse le crayon.
+narrateur|Il le tend.
+copine|Merci, Nino.
+narrateur|Sarah reprend le crayon.
+narrateur|Elle le pose dans la boîte, tout droit.
+narrateur|La maîtresse s'approche.
+maitresse|On aide.
+maitresse|On n'est pas là pour rire.
+maitresse|On n'est pas là pour répéter.
+enfant-m|On aide.
+narrateur|Plus tard, le parc sent l'herbe coupée.
+narrateur|Une chaîne de balançoire tinte, loin.
+narrateur|Un grain de sable brille sur le bac.
+narrateur|Maman tient le gant de Nino.
+maman|Tu te souviens du crayon ?
+enfant-m|Oui.
+enfant-m|On ramasse.
+narrateur|Sarah laisse tomber son gant bleu.
+narrateur|Le gant est mou, près du bac.
+narrateur|Un autre petit rire commence.
+narrateur|Le rire est court.
+narrateur|Nino se souvient.
+narrateur|Il n'est pas là pour rire.
+narrateur|Il ne répète pas.
+enfant-m|Ce n'est pas gentil.
+narrateur|Il tend le gant.
+copine|Merci.
+maman|Tu as repris le geste.
+maman|Même leçon, autre lieu.
+maman|Il ne faut pas rire.
+maman|Il ne faut pas répéter.
+maman|Ce n'est pas gentil.
+maman|C'est du bon travail, Nino.
+maman|Tu as du sable sur les genoux ?
+enfant-m|Un peu.
+maman|On le secoue.
+narrateur|Nino serre la main de maman.
+narrateur|Le gant bleu est remis.
+narrateur|Le rayon du matin n'est plus là.
+narrateur|Il reste l'herbe, et le calme.
+maman|On rentre tout doux ?
+enfant-m|Oui, maman.
+narrateur|Un oiseau crie, puis plus.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1508,7 +1576,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade rit. Que fait Nino ?</t>
+          <t>narrateur|Un camarade rit.
+narrateur|Que fait Nino ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino n'a pas ri. Il n'a pas répété. Il Ce n'est pas gentil. À l'école, puis au parc.</t>
+          <t>Nino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis au parc. Tu as ramassé le crayon. Puis le gant. Bravo. C'est du bon travail. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,8 +1749,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino n'a pas ri. Il n'a pas répété. Il
-enfant-f|Ce n'est pas gentil. À l'école, puis au parc.</t>
+          <t>narrateur|Nino n'a pas ri.
+narrateur|Il n'a pas répété.
+narrateur|Il a dit : ce n'est pas gentil.
+narrateur|À l'école, puis au parc.
+maman|Tu as ramassé le crayon.
+maman|Puis le gant.
+maman|Bravo.
+maman|C'est du bon travail.
+enfant-m|On aide.
+enfant-m|Deux fois.
+maman|Oui.
+maman|Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1713,7 +1792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino range son cartable. Maman marche à côté.</t>
+          <t>Nino range son cartable près du portail. Le zip chante un peu. Tu as fini de ranger ? Oui, maman. Le gant de Sarah est au chaud. On rentre ? Oui. Maman marche à côté. L'herbe sent encore fort. La chaîne de balançoire tinte, plus loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1849,7 +1928,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nino range son cartable. Maman marche à côté.</t>
+          <t>narrateur|Nino range son cartable près du portail.
+narrateur|Le zip chante un peu.
+maman|Tu as fini de ranger ?
+enfant-m|Oui, maman.
+maman|Le gant de Sarah est au chaud.
+maman|On rentre ?
+enfant-m|Oui.
+narrateur|Maman marche à côté.
+narrateur|L'herbe sent encore fort.
+narrateur|La chaîne de balançoire tinte, plus loin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1877,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai ramassé. À l'école, puis au parc. Bravo. Tu as fait du bon travail. Le crayon jaune est dans la boîte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2017,7 +2105,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai ramassé.
+enfant-m|À l'école, puis au parc.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le crayon jaune est dans la boîte.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2039,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon de poussière danse au-dessus des crayons. La boîte en bois est chaude au soleil. Ça sent le crayon gras et le savon. Le plancher craque un peu. Nino, ta veste est sur le crochet. Tu as vu le rayon sur les crayons ? Oui, maman. Il brille. Je reviens te chercher après l'école. On ira au parc. D'accord. En ce moment, la classe range les crayons. Sarah tient un crayon jaune. Le bois est lisse. Le crayon glisse. Il tombe près de la boîte. Un camarade commence un petit rire. Le rire est court. Nino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Sarah. Il ramasse le crayon. Il le tend. Merci, Nino. Sarah reprend le crayon. Elle le pose dans la boîte, tout droit. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, le parc sent l'herbe coupée. Une chaîne de balançoire tinte, loin. Un grain de sable brille sur le bac. Maman tient le gant de Nino. Tu te souviens du crayon ? Oui. On ramasse. Sarah laisse tomber son gant bleu. Le gant est mou, près du bac. Un autre petit rire commence. Le rire est court. Nino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il tend le gant. Merci. Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. C'est du bon travail, Nino. Tu as du sable sur les genoux ? Un peu. On le secoue. Nino serre la main de maman. Le gant bleu est remis. Le rayon du matin n'est plus là. Il reste l'herbe, et le calme. On rentre tout doux ? Oui, maman. Un oiseau crie, puis plus.</t>
+          <t>Un rayon de poussière danse au-dessus des crayons. La boîte en bois est chaude au soleil. Ça sent le crayon gras et le savon. Le plancher craque un peu. Nino, ta veste est sur le crochet. Tu as vu le rayon sur les crayons ? Oui, maman. Il brille. Je reviens te chercher après l'école. On ira au parc. D'accord. En ce moment, la classe range les crayons. Sarah tient un crayon jaune. Le bois est lisse. Le crayon glisse. Il tombe près de la boîte. Un camarade commence un petit rire. Le rire est court. Nino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Sarah. Il ramasse le crayon. Il le tend. Merci, Nino. Sarah reprend le crayon. Elle le pose dans la boîte, tout droit. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, le parc sent l'herbe coupée. Une chaîne de balançoire tinte, loin. Un grain de sable brille sur le bac. Maman tient le gant de Nino. Tu te souviens du crayon ? Oui. On ramasse. Sarah laisse tomber son gant bleu. Le gant est mou, près du bac. Un autre petit rire commence. Le rire est court. Nino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il tend le gant. Merci. Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as du sable sur les genoux ? Un peu. On le secoue. Nino serre la main de maman. Le gant bleu est remis. Le rayon du matin n'est plus là. Il reste l'herbe, et le calme. On rentre tout doux ? Oui, maman. Un oiseau crie, puis plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino est à l'école. La classe range les crayons. Le couloir sent le savon. Zoé laisse tomber un crayon. Un camarade commence à rire. Le rire est court. Nino ne rit &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt;. Il ne faut pas rire. Nino ne répète pas. Il ne faut pas répéter. Nino dit : ce n'est pas gentil. Il va vers Zoé. Il ramasse le crayon. Il le tend. Zoé le reprend. La maîtresse s'approche. Le camarade dit : pardon. Plus tard, Nino est au parc avec maman. Un enfant laisse tomber son gant. Un autre commence à rire. Le rire est court. Nino se souvient. Il ne rit pas. Il ne répète pas. Il dit : ce n'est pas gentil. Il tend le gant. Maman dit : tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Nino serre la main de maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon de poussière danse au-dessus des crayons. La boîte en bois est chaude au soleil. Ça sent le crayon gras et le savon. Le plancher craque un peu. Nino, ta veste est sur le crochet. Tu as vu le rayon sur les crayons ? Oui, maman. Il brille. Je reviens te chercher après l'école. On ira au parc. D'accord. En ce moment, la classe range les crayons. Sarah tient un crayon jaune. Le bois est lisse. Le crayon glisse. Il tombe près de la boîte. Un camarade commence un petit rire. Le rire est court. Nino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Sarah. Il ramasse le crayon. Il le tend. Merci, Nino. Sarah reprend le crayon. Elle le pose dans la boîte, tout droit. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, le parc sent l'herbe coupée. Une chaîne de balançoire tinte, loin. Un grain de sable brille sur le bac. Maman tient le gant de Nino. Tu te souviens du crayon ? Oui. On ramasse. Sarah laisse tomber son gant bleu. Le gant est mou, près du bac. Un autre petit rire commence. Le rire est court. Nino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il tend le gant. Merci. Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as du sable sur les genoux ? Un peu. On le secoue. Nino serre la main de maman. Le gant bleu est remis. Le rayon du matin n'est plus là. Il reste l'herbe, et le calme. On rentre tout doux ? Oui, maman. Un oiseau crie, puis plus.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1378,7 +1378,6 @@
 maman|Il ne faut pas rire.
 maman|Il ne faut pas répéter.
 maman|Ce n'est pas gentil.
-maman|C'est du bon travail, Nino.
 maman|Tu as du sable sur les genoux ?
 enfant-m|Un peu.
 maman|On le secoue.
@@ -1425,7 +1424,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un camarade rit. Que fait Nino ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade rit. Que fait Nino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1580,7 +1579,6 @@
 narrateur|Que fait Nino ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1605,12 +1603,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis au parc. Tu as ramassé le crayon. Puis le gant. Bravo. C'est du bon travail. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
+          <t>Nino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis au parc. Tu as ramassé le crayon. Puis le gant. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino n'a &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis au parc.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis au parc. Tu as ramassé le crayon. Puis le gant. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1756,7 +1754,6 @@
 maman|Tu as ramassé le crayon.
 maman|Puis le gant.
 maman|Bravo.
-maman|C'est du bon travail.
 enfant-m|On aide.
 enfant-m|Deux fois.
 maman|Oui.
@@ -1797,7 +1794,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino range son cartable. Maman marche à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino range son cartable près du portail. Le zip chante un peu. Tu as fini de ranger ? Oui, maman. Le gant de Sarah est au chaud. On rentre ? Oui. Maman marche à côté. L'herbe sent encore fort. La chaîne de balançoire tinte, plus loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1940,7 +1937,6 @@
 narrateur|La chaîne de balançoire tinte, plus loin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé. À l'école, puis au parc. Bravo. Tu as fait du bon travail. Le crayon jaune est dans la boîte. L'histoire est finie.</t>
+          <t>J'ai ramassé. À l'école, puis au parc. Bravo. Le crayon jaune est dans la boîte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai ramassé. À l'école, puis au parc. Bravo. Le crayon jaune est dans la boîte.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,12 +2104,9 @@
           <t>enfant-m|J'ai ramassé.
 enfant-m|À l'école, puis au parc.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le crayon jaune est dans la boîte.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le crayon jaune est dans la boîte.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2170,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nino, Zoé, maman</t>
+          <t>Nino, Sarah, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-02.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le crayon et le gant de Nino</t>
+          <t>Le crayon jaune au soleil</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école puis parc</t>
+          <t>classe, boîte de crayons, puis parc</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Un crayon tombe en classe, puis un gant au parc. Nino n'est pas là pour rire. Il ramasse, il tend, deux fois.</t>
+          <t>Nino veut dessiner un soleil avec Sarah. Le crayon jaune tombe. Un rire commence. Sarah a le visage triste. Nino s'arrête, tend le crayon. Ils dessinent. Au parc, le gant tombe. Même geste vécu. Ils jouent au sable.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon de poussière danse au-dessus des crayons. La boîte en bois est chaude au soleil. Ça sent le crayon gras et le savon. Le plancher craque un peu. Nino, ta veste est sur le crochet. Tu as vu le rayon sur les crayons ? Oui, maman. Il brille. Je reviens te chercher après l'école. On ira au parc. D'accord. En ce moment, la classe range les crayons. Sarah tient un crayon jaune. Le bois est lisse. Le crayon glisse. Il tombe près de la boîte. Un camarade commence un petit rire. Le rire est court. Nino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Sarah. Il ramasse le crayon. Il le tend. Merci, Nino. Sarah reprend le crayon. Elle le pose dans la boîte, tout droit. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, le parc sent l'herbe coupée. Une chaîne de balançoire tinte, loin. Un grain de sable brille sur le bac. Maman tient le gant de Nino. Tu te souviens du crayon ? Oui. On ramasse. Sarah laisse tomber son gant bleu. Le gant est mou, près du bac. Un autre petit rire commence. Le rire est court. Nino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il tend le gant. Merci. Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as du sable sur les genoux ? Un peu. On le secoue. Nino serre la main de maman. Le gant bleu est remis. Le rayon du matin n'est plus là. Il reste l'herbe, et le calme. On rentre tout doux ? Oui, maman. Un oiseau crie, puis plus.</t>
+          <t>La boîte des crayons sent le bois chaud. Un rayon de poussière danse au-dessus. Ça sent le crayon gras et le savon. Le plancher craque un peu. Nino, ta veste est sur le crochet. Tu as vu le rayon sur les crayons ? Oui, maman. Il brille. Je reviens te chercher après l'école. On ira au parc. D'accord. Maman part vers la porte. En ce moment, Nino prend un crayon jaune. Le bois est lisse, encore chaud. Sarah, on dessine le soleil ? Oui. Sarah tient le crayon. Le crayon glisse. Il tombe près de la boîte. Un petit rire commence dans la gorge de Nino. Sarah baisse les yeux. Sa bouche devient toute petite. Le crayon reste par terre. Nino referme la bouche. Le rire ne sort plus. Il ramasse le crayon jaune. Il le tend. Merci, Nino. Sarah reprend le crayon. On dessine ? Oui. Le jaune pose un rond sur le papier. La maîtresse s'approche. Vous dessinez le soleil ? Oui. Il est bien rond. Plus tard, le parc sent l'herbe coupée. Une chaîne de balançoire tinte, loin. Un grain de sable brille sur le bac. Maman tient le gant de Nino. Tu veux le bac à sable ? Oui. Avec Sarah. Sarah a un gant bleu. Le gant glisse. Il tombe, mou, près du bac. Un petit rire recommence, tout court. Sarah regarde le gant. Ses joues baissent. Nino referme encore la bouche. Il ramasse le gant. La laine est froide, un peu humide. Il le tend. Merci. On fait un gâteau de sable ? Oui. Le sable coule entre leurs doigts. Le gant bleu est remis. Vous jouez ensemble ? Oui, maman. Bravo, Nino. Tu as du sable sur les genoux ? Un peu. On le secoue ? Oui. Nino serre la main de maman. Il reste l'herbe, et le calme. On rentre tout doux ? Oui, maman. Un oiseau crie, puis plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Un rayon de poussière danse au-dessus des crayons. La boîte en bois est chaude au soleil. Ça sent le crayon gras et le savon. Le plancher craque un peu. Nino, ta veste est sur le crochet. Tu as vu le rayon sur les crayons ? Oui, maman. Il brille. Je reviens te chercher après l'école. On ira au parc. D'accord. En ce moment, la classe range les crayons. Sarah tient un crayon jaune. Le bois est lisse. Le crayon glisse. Il tombe près de la boîte. Un camarade commence un petit rire. Le rire est court. Nino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Sarah. Il ramasse le crayon. Il le tend. Merci, Nino. Sarah reprend le crayon. Elle le pose dans la boîte, tout droit. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, le parc sent l'herbe coupée. Une chaîne de balançoire tinte, loin. Un grain de sable brille sur le bac. Maman tient le gant de Nino. Tu te souviens du crayon ? Oui. On ramasse. Sarah laisse tomber son gant bleu. Le gant est mou, près du bac. Un autre petit rire commence. Le rire est court. Nino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il tend le gant. Merci. Tu as repris le geste. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as du sable sur les genoux ? Un peu. On le secoue. Nino serre la main de maman. Le gant bleu est remis. Le rayon du matin n'est plus là. Il reste l'herbe, et le calme. On rentre tout doux ? Oui, maman. Un oiseau crie, puis plus.</t>
+          <t>La boîte des crayons sent le bois chaud. Un rayon de poussière danse au-dessus. Ça sent le crayon gras et le savon. Le plancher craque un peu. Nino, ta veste est sur le crochet. Tu as vu le rayon sur les crayons ? Oui, maman. Il brille. Je reviens te chercher après l'école. On ira au parc. D'accord. Maman part vers la porte. En ce moment, Nino prend un crayon jaune. Le bois est lisse, encore chaud. Sarah, on dessine le soleil ? Oui. Sarah tient le crayon. Le crayon glisse. Il tombe près de la boîte. Un petit rire commence dans la gorge de Nino. Sarah baisse les yeux. Sa bouche devient toute petite. Le crayon reste par terre. Nino referme la bouche. Le rire ne sort plus. Il ramasse le crayon jaune. Il le tend. Merci, Nino. Sarah reprend le crayon. On dessine ? Oui. Le jaune pose un rond sur le papier. La maîtresse s'approche. Vous dessinez le soleil ? Oui. Il est bien rond. Plus tard, le parc sent l'herbe coupée. Une chaîne de balançoire tinte, loin. Un grain de sable brille sur le bac. Maman tient le gant de Nino. Tu veux le bac à sable ? Oui. Avec Sarah. Sarah a un gant bleu. Le gant glisse. Il tombe, mou, près du bac. Un petit rire recommence, tout court. Sarah regarde le gant. Ses joues baissent. Nino referme encore la bouche. Il ramasse le gant. La laine est froide, un peu humide. Il le tend. Merci. On fait un gâteau de sable ? Oui. Le sable coule entre leurs doigts. Le gant bleu est remis. Vous jouez ensemble ? Oui, maman. Bravo, Nino. Tu as du sable sur les genoux ? Un peu. On le secoue ? Oui. Nino serre la main de maman. Il reste l'herbe, et le calme. On rentre tout doux ? Oui, maman. Un oiseau crie, puis plus.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,8 +1324,8 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Un rayon de poussière danse au-dessus des crayons.
-narrateur|La boîte en bois est chaude au soleil.
+          <t>narrateur|La boîte des crayons sent le bois chaud.
+narrateur|Un rayon de poussière danse au-dessus.
 narrateur|Ça sent le crayon gras et le savon.
 narrateur|Le plancher craque un peu.
 maman|Nino, ta veste est sur le crochet.
@@ -1335,55 +1335,61 @@
 maman|Je reviens te chercher après l'école.
 maman|On ira au parc.
 enfant-m|D'accord.
-narrateur|En ce moment, la classe range les crayons.
-narrateur|Sarah tient un crayon jaune.
-narrateur|Le bois est lisse.
+narrateur|Maman part vers la porte.
+narrateur|En ce moment, Nino prend un crayon jaune.
+narrateur|Le bois est lisse, encore chaud.
+enfant-m|Sarah, on dessine le soleil ?
+copine|Oui.
+narrateur|Sarah tient le crayon.
 narrateur|Le crayon glisse.
 narrateur|Il tombe près de la boîte.
-narrateur|Un camarade commence un petit rire.
-narrateur|Le rire est court.
-narrateur|Nino n'est pas là pour rire.
-narrateur|Il ne répète pas.
-enfant-m|Ce n'est pas gentil.
-narrateur|Il va vers Sarah.
-narrateur|Il ramasse le crayon.
+narrateur|Un petit rire commence dans la gorge de Nino.
+narrateur|Sarah baisse les yeux.
+narrateur|Sa bouche devient toute petite.
+narrateur|Le crayon reste par terre.
+narrateur|Nino referme la bouche.
+narrateur|Le rire ne sort plus.
+narrateur|Il ramasse le crayon jaune.
 narrateur|Il le tend.
 copine|Merci, Nino.
 narrateur|Sarah reprend le crayon.
-narrateur|Elle le pose dans la boîte, tout droit.
+enfant-m|On dessine ?
+copine|Oui.
+narrateur|Le jaune pose un rond sur le papier.
 narrateur|La maîtresse s'approche.
-maitresse|On aide.
-maitresse|On n'est pas là pour rire.
-maitresse|On n'est pas là pour répéter.
-enfant-m|On aide.
+maitresse|Vous dessinez le soleil ?
+enfant-m|Oui.
+maitresse|Il est bien rond.
 narrateur|Plus tard, le parc sent l'herbe coupée.
 narrateur|Une chaîne de balançoire tinte, loin.
 narrateur|Un grain de sable brille sur le bac.
 narrateur|Maman tient le gant de Nino.
-maman|Tu te souviens du crayon ?
+maman|Tu veux le bac à sable ?
 enfant-m|Oui.
-enfant-m|On ramasse.
-narrateur|Sarah laisse tomber son gant bleu.
-narrateur|Le gant est mou, près du bac.
-narrateur|Un autre petit rire commence.
-narrateur|Le rire est court.
-narrateur|Nino se souvient.
-narrateur|Il n'est pas là pour rire.
-narrateur|Il ne répète pas.
-enfant-m|Ce n'est pas gentil.
-narrateur|Il tend le gant.
+enfant-m|Avec Sarah.
+narrateur|Sarah a un gant bleu.
+narrateur|Le gant glisse.
+narrateur|Il tombe, mou, près du bac.
+narrateur|Un petit rire recommence, tout court.
+narrateur|Sarah regarde le gant.
+narrateur|Ses joues baissent.
+narrateur|Nino referme encore la bouche.
+narrateur|Il ramasse le gant.
+narrateur|La laine est froide, un peu humide.
+narrateur|Il le tend.
 copine|Merci.
-maman|Tu as repris le geste.
-maman|Même leçon, autre lieu.
-maman|Il ne faut pas rire.
-maman|Il ne faut pas répéter.
-maman|Ce n'est pas gentil.
+enfant-m|On fait un gâteau de sable ?
+copine|Oui.
+narrateur|Le sable coule entre leurs doigts.
+narrateur|Le gant bleu est remis.
+maman|Vous jouez ensemble ?
+enfant-m|Oui, maman.
+maman|Bravo, Nino.
 maman|Tu as du sable sur les genoux ?
 enfant-m|Un peu.
-maman|On le secoue.
+maman|On le secoue ?
+enfant-m|Oui.
 narrateur|Nino serre la main de maman.
-narrateur|Le gant bleu est remis.
-narrateur|Le rayon du matin n'est plus là.
 narrateur|Il reste l'herbe, et le calme.
 maman|On rentre tout doux ?
 enfant-m|Oui, maman.
@@ -1439,7 +1445,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>pas rire | pas gentil | ne pas rire | pas répéter</t>
+          <t>pas rire | pas gentil | ne pas rire | pas répéter | ramasse | il ramasse | il tend</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1454,7 +1460,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il ne rit pas. Il dit que ce n'est pas gentil. Que fait Nino ?</t>
+          <t>Nino voit le visage de Sarah. Que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1496,14 +1502,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1603,12 +1609,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis au parc. Tu as ramassé le crayon. Puis le gant. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
+          <t>Nino a vu le visage de Sarah. Le rire s'est arrêté. Il a tendu le crayon, puis le gant. Bravo. Vous avez dessiné, puis joué. Le soleil, et le sable. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis au parc. Tu as ramassé le crayon. Puis le gant. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
+          <t>Nino a vu le visage de Sarah. Le rire s'est arrêté. Il a tendu le crayon, puis le gant. Bravo. Vous avez dessiné, puis joué. Le soleil, et le sable. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1671,7 +1677,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1747,17 +1753,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino n'a pas ri.
-narrateur|Il n'a pas répété.
-narrateur|Il a dit : ce n'est pas gentil.
-narrateur|À l'école, puis au parc.
-maman|Tu as ramassé le crayon.
-maman|Puis le gant.
+          <t>narrateur|Nino a vu le visage de Sarah.
+narrateur|Le rire s'est arrêté.
+narrateur|Il a tendu le crayon, puis le gant.
 maman|Bravo.
-enfant-m|On aide.
-enfant-m|Deux fois.
-maman|Oui.
-maman|Même geste, autre lieu.</t>
+maman|Vous avez dessiné, puis joué.
+enfant-m|Le soleil, et le sable.
+maman|Oui.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1789,12 +1791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino range son cartable près du portail. Le zip chante un peu. Tu as fini de ranger ? Oui, maman. Le gant de Sarah est au chaud. On rentre ? Oui. Maman marche à côté. L'herbe sent encore fort. La chaîne de balançoire tinte, plus loin.</t>
+          <t>Nino range son cartable près du portail. Le zip chante un peu. Tu as fini de ranger ? Oui, maman. Le gant de Sarah est au chaud. On rentre ? Oui. Maman marche à côté. L'herbe sent encore fort. Le soleil est sur le papier, à la classe ? Oui, tout rond. La chaîne de balançoire tinte, plus loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nino range son cartable près du portail. Le zip chante un peu. Tu as fini de ranger ? Oui, maman. Le gant de Sarah est au chaud. On rentre ? Oui. Maman marche à côté. L'herbe sent encore fort. La chaîne de balançoire tinte, plus loin.</t>
+          <t>Nino range son cartable près du portail. Le zip chante un peu. Tu as fini de ranger ? Oui, maman. Le gant de Sarah est au chaud. On rentre ? Oui. Maman marche à côté. L'herbe sent encore fort. Le soleil est sur le papier, à la classe ? Oui, tout rond. La chaîne de balançoire tinte, plus loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1857,7 +1859,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1934,6 +1936,8 @@
 enfant-m|Oui.
 narrateur|Maman marche à côté.
 narrateur|L'herbe sent encore fort.
+maman|Le soleil est sur le papier, à la classe ?
+enfant-m|Oui, tout rond.
 narrateur|La chaîne de balançoire tinte, plus loin.</t>
         </is>
       </c>
@@ -1961,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé. À l'école, puis au parc. Bravo. Le crayon jaune est dans la boîte.</t>
+          <t>On a dessiné. Puis le sable. Bravo. Le crayon jaune est dans la boîte, au chaud.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé. À l'école, puis au parc. Bravo. Le crayon jaune est dans la boîte.</t>
+          <t>On a dessiné. Puis le sable. Bravo. Le crayon jaune est dans la boîte, au chaud.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2029,7 +2033,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2101,10 +2105,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai ramassé.
-enfant-m|À l'école, puis au parc.
+          <t>enfant-m|On a dessiné.
+enfant-m|Puis le sable.
 maman|Bravo.
-narrateur|Le crayon jaune est dans la boîte.</t>
+narrateur|Le crayon jaune est dans la boîte, au chaud.</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2179,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
